--- a/World Cup 2026 SweepStake Template.xlsx
+++ b/World Cup 2026 SweepStake Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvfile01\Users\bobby.blaney\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7878203-6AD8-4B8A-89E1-FB10CFD03A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8298577-4561-4939-AADD-8947DCDE8CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -551,7 +551,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="182">
   <si>
     <t>Sweepstake 1</t>
   </si>
@@ -734,9 +734,6 @@
     <t>GD</t>
   </si>
   <si>
-    <t>3rd Place Table</t>
-  </si>
-  <si>
     <t>Mexico</t>
   </si>
   <si>
@@ -1197,6 +1194,40 @@
   </si>
   <si>
     <t>Final</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+Using the group tables, add in the points each team gained for each of their games
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Win = 3    Draw = 1    Loss = 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Goal difference will need to be manually added, and can be found in the live group tables.
+Biggest defeat is to record each teams biggest loss, to identify the bogey prize winner for this category.
+Winners for each group, Runner up and 3rd place will all auto populate to help you fill in the Knockouts table</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1207,7 +1238,7 @@
     <numFmt numFmtId="6" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0.0;[Red]\-&quot;£&quot;#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1234,6 +1265,21 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1249,7 +1295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -1819,11 +1865,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1936,10 +2101,8 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1984,6 +2147,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3685,16 +3884,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>22393</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>160611</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>470068</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>65361</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>170866</xdr:rowOff>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>75616</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3723,7 +3922,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4289593" y="351111"/>
+          <a:off x="4127668" y="446361"/>
           <a:ext cx="6130757" cy="1534255"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5207,7 +5406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:Y71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -5216,7 +5415,7 @@
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
@@ -5247,13 +5446,24 @@
       <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="80" t="s">
+        <v>180</v>
+      </c>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="82"/>
+    </row>
+    <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>27</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5265,16 +5475,30 @@
       <c r="F2" s="13"/>
       <c r="G2" s="14"/>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J2" t="str" cm="1">
         <f t="array" ref="J2">INDEX(A2:A5,MATCH(LARGE(B2:B5+C2:C5+D2:D5,1),B2:B5+C2:C5+D2:D5,0))</f>
         <v>Mexico</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N2" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="85"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5292,10 +5516,22 @@
         <f t="array" ref="J3">INDEX(A2:A5,MATCH(LARGE(B2:B5+C2:C5+D2:D5,2),B2:B5+C2:C5+D2:D5,0))</f>
         <v>Mexico</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N3" s="86"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="87"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -5307,7 +5543,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="4"/>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" t="str" cm="1">
         <f t="array" ref="J4">INDEX(A3:A6,MATCH(LARGE(B3:B6+C3:C6+D3:D6,3),B3:B6+C3:C6+D3:D6,0))</f>
@@ -5317,10 +5553,22 @@
         <f>LARGE(E2:E5,3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="86"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="79"/>
+      <c r="W4" s="79"/>
+      <c r="X4" s="79"/>
+      <c r="Y4" s="87"/>
+    </row>
+    <row r="5" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -5331,8 +5579,20 @@
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N5" s="86"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
+      <c r="W5" s="79"/>
+      <c r="X5" s="79"/>
+      <c r="Y5" s="87"/>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5340,10 +5600,22 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N6" s="86"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
+      <c r="V6" s="79"/>
+      <c r="W6" s="79"/>
+      <c r="X6" s="79"/>
+      <c r="Y6" s="87"/>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>20</v>
@@ -5364,12 +5636,24 @@
         <v>14</v>
       </c>
       <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="86"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="79"/>
+      <c r="S7" s="79"/>
+      <c r="T7" s="79"/>
+      <c r="U7" s="79"/>
+      <c r="V7" s="79"/>
+      <c r="W7" s="79"/>
+      <c r="X7" s="79"/>
+      <c r="Y7" s="87"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -5381,16 +5665,28 @@
       <c r="F8" s="1"/>
       <c r="G8" s="4"/>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J8" t="str" cm="1">
         <f t="array" ref="J8">INDEX(A8:A11,MATCH(LARGE(B8:B11+C8:C11+D8:D11,1),B8:B11+C8:C11+D8:D11,0))</f>
         <v>Canada</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N8" s="86"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="79"/>
+      <c r="R8" s="79"/>
+      <c r="S8" s="79"/>
+      <c r="T8" s="79"/>
+      <c r="U8" s="79"/>
+      <c r="V8" s="79"/>
+      <c r="W8" s="79"/>
+      <c r="X8" s="79"/>
+      <c r="Y8" s="87"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -5408,10 +5704,22 @@
         <f t="array" ref="J9">INDEX(A8:A11,MATCH(LARGE(B8:B11+C8:C11+D8:D11,2),B8:B11+C8:C11+D8:D11,0))</f>
         <v>Canada</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N9" s="86"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
+      <c r="R9" s="79"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="79"/>
+      <c r="U9" s="79"/>
+      <c r="V9" s="79"/>
+      <c r="W9" s="79"/>
+      <c r="X9" s="79"/>
+      <c r="Y9" s="87"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -5423,7 +5731,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="4"/>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J10" t="str" cm="1">
         <f t="array" ref="J10">INDEX(A9:A12,MATCH(LARGE(B9:B12+C9:C12+D9:D12,3),B9:B12+C9:C12+D9:D12,0))</f>
@@ -5433,10 +5741,22 @@
         <f>LARGE(E8:E11,3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="86"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="79"/>
+      <c r="T10" s="79"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="79"/>
+      <c r="W10" s="79"/>
+      <c r="X10" s="79"/>
+      <c r="Y10" s="87"/>
+    </row>
+    <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -5447,8 +5767,20 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N11" s="86"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="79"/>
+      <c r="V11" s="79"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="79"/>
+      <c r="Y11" s="87"/>
+    </row>
+    <row r="12" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -5456,10 +5788,22 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N12" s="86"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="79"/>
+      <c r="Q12" s="79"/>
+      <c r="R12" s="79"/>
+      <c r="S12" s="79"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="79"/>
+      <c r="W12" s="79"/>
+      <c r="X12" s="79"/>
+      <c r="Y12" s="87"/>
+    </row>
+    <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>20</v>
@@ -5480,12 +5824,24 @@
         <v>14</v>
       </c>
       <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="88"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="89"/>
+      <c r="T13" s="89"/>
+      <c r="U13" s="89"/>
+      <c r="V13" s="89"/>
+      <c r="W13" s="89"/>
+      <c r="X13" s="89"/>
+      <c r="Y13" s="90"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -5497,16 +5853,16 @@
       <c r="F14" s="1"/>
       <c r="G14" s="4"/>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J14" t="str" cm="1">
         <f t="array" ref="J14">INDEX(A14:A17,MATCH(LARGE(B14:B17+C14:C17+D14:D17,1),B14:B17+C14:C17+D14:D17,0))</f>
         <v>Brasil</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -5525,9 +5881,9 @@
         <v>Brasil</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -5539,7 +5895,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="4"/>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J16" t="str" cm="1">
         <f t="array" ref="J16">INDEX(A15:A18,MATCH(LARGE(B15:B18+C15:C18+D15:D18,3),B15:B18+C15:C18+D15:D18,0))</f>
@@ -5552,7 +5908,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -5575,7 +5931,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>20</v>
@@ -5596,12 +5952,12 @@
         <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5613,7 +5969,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="4"/>
       <c r="I20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J20" t="str" cm="1">
         <f t="array" ref="J20">INDEX(A20:A23,MATCH(LARGE(B20:B23+C20:C23+D20:D23,1),B20:B23+C20:C23+D20:D23,0))</f>
@@ -5622,7 +5978,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5643,7 +5999,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5655,7 +6011,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J22" t="str" cm="1">
         <f t="array" ref="J22">INDEX(A21:A24,MATCH(LARGE(B21:B24+C21:C24+D21:D24,3),B21:B24+C21:C24+D21:D24,0))</f>
@@ -5668,7 +6024,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -5691,7 +6047,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>20</v>
@@ -5712,12 +6068,12 @@
         <v>14</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5729,7 +6085,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="4"/>
       <c r="I26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J26" t="str" cm="1">
         <f t="array" ref="J26">INDEX(A26:A29,MATCH(LARGE(B26:B29+C26:C29+D26:D29,1),B26:B29+C26:C29+D26:D29,0))</f>
@@ -5738,7 +6094,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5759,7 +6115,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5771,7 +6127,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="4"/>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J28" t="str" cm="1">
         <f t="array" ref="J28">INDEX(A27:A30,MATCH(LARGE(B27:B30+C27:C30+D27:D30,3),B27:B30+C27:C30+D27:D30,0))</f>
@@ -5784,7 +6140,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -5807,7 +6163,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>20</v>
@@ -5828,12 +6184,12 @@
         <v>14</v>
       </c>
       <c r="I31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5845,7 +6201,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="4"/>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J32" t="str" cm="1">
         <f t="array" ref="J32">INDEX(A32:A35,MATCH(LARGE(B32:B35+C32:C35+D32:D35,1),B32:B35+C32:C35+D32:D35,0))</f>
@@ -5854,7 +6210,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5875,7 +6231,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5887,7 +6243,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="4"/>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J34" t="str" cm="1">
         <f t="array" ref="J34">INDEX(A33:A36,MATCH(LARGE(B33:B36+C33:C36+D33:D36,3),B33:B36+C33:C36+D33:D36,0))</f>
@@ -5900,7 +6256,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -5923,7 +6279,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>20</v>
@@ -5944,12 +6300,12 @@
         <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -5961,7 +6317,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="4"/>
       <c r="I38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J38" t="str" cm="1">
         <f t="array" ref="J38">INDEX(A38:A41,MATCH(LARGE(B38:B41+C38:C41+D38:D41,1),B38:B41+C38:C41+D38:D41,0))</f>
@@ -5970,7 +6326,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -5991,7 +6347,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -6003,7 +6359,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="4"/>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J40" t="str" cm="1">
         <f t="array" ref="J40">INDEX(A39:A42,MATCH(LARGE(B39:B42+C39:C42+D39:D42,3),B39:B42+C39:C42+D39:D42,0))</f>
@@ -6016,7 +6372,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -6039,7 +6395,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>20</v>
@@ -6060,12 +6416,12 @@
         <v>14</v>
       </c>
       <c r="I43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -6077,7 +6433,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="4"/>
       <c r="I44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J44" t="str" cm="1">
         <f t="array" ref="J44">INDEX(A44:A47,MATCH(LARGE(B44:B47+C44:C47+D44:D47,1),B44:B47+C44:C47+D44:D47,0))</f>
@@ -6086,7 +6442,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -6107,7 +6463,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -6119,7 +6475,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="4"/>
       <c r="I46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J46" t="str" cm="1">
         <f t="array" ref="J46">INDEX(A45:A48,MATCH(LARGE(B45:B48+C45:C48+D45:D48,3),B45:B48+C45:C48+D45:D48,0))</f>
@@ -6132,7 +6488,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -6155,7 +6511,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>20</v>
@@ -6176,12 +6532,12 @@
         <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -6193,7 +6549,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="4"/>
       <c r="I50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J50" t="str" cm="1">
         <f t="array" ref="J50">INDEX(A50:A53,MATCH(LARGE(B50:B53+C50:C53+D50:D53,1),B50:B53+C50:C53+D50:D53,0))</f>
@@ -6202,7 +6558,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -6223,7 +6579,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -6235,7 +6591,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="4"/>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J52" t="str" cm="1">
         <f t="array" ref="J52">INDEX(A51:A54,MATCH(LARGE(B51:B54+C51:C54+D51:D54,3),B51:B54+C51:C54+D51:D54,0))</f>
@@ -6248,7 +6604,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -6271,7 +6627,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>20</v>
@@ -6292,12 +6648,12 @@
         <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -6309,7 +6665,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="4"/>
       <c r="I56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J56" t="str" cm="1">
         <f t="array" ref="J56">INDEX(A56:A59,MATCH(LARGE(B56:B59+C56:C59+D56:D59,1),B56:B59+C56:C59+D56:D59,0))</f>
@@ -6318,7 +6674,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -6339,7 +6695,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -6351,7 +6707,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="4"/>
       <c r="I58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J58" t="str" cm="1">
         <f t="array" ref="J58">INDEX(A57:A60,MATCH(LARGE(B57:B60+C57:C60+D57:D60,3),B57:B60+C57:C60+D57:D60,0))</f>
@@ -6364,7 +6720,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -6387,7 +6743,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>20</v>
@@ -6408,12 +6764,12 @@
         <v>14</v>
       </c>
       <c r="I61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -6425,7 +6781,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="4"/>
       <c r="I62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J62" t="str" cm="1">
         <f t="array" ref="J62">INDEX(A62:A65,MATCH(LARGE(B62:B65+C62:C65+D62:D65,1),B62:B65+C62:C65+D62:D65,0))</f>
@@ -6434,7 +6790,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -6455,7 +6811,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -6467,7 +6823,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="4"/>
       <c r="I64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J64" t="str" cm="1">
         <f t="array" ref="J64">INDEX(A63:A66,MATCH(LARGE(B63:B66+C63:C66+D63:D66,3),B63:B66+C63:C66+D63:D66,0))</f>
@@ -6480,7 +6836,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -6503,7 +6859,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>20</v>
@@ -6524,12 +6880,12 @@
         <v>14</v>
       </c>
       <c r="I67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6541,7 +6897,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="4"/>
       <c r="I68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J68" t="str" cm="1">
         <f t="array" ref="J68">INDEX(A68:A71,MATCH(LARGE(B68:B71+C68:C71+D68:D71,1),B68:B71+C68:C71+D68:D71,0))</f>
@@ -6550,7 +6906,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -6571,7 +6927,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -6583,7 +6939,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="4"/>
       <c r="I70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J70" t="str" cm="1">
         <f t="array" ref="J70">INDEX(A69:A72,MATCH(LARGE(B69:B72+C69:C72+D69:D72,3),B69:B72+C69:C72+D69:D72,0))</f>
@@ -6596,7 +6952,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -6613,6 +6969,10 @@
   <protectedRanges>
     <protectedRange sqref="B2:D5 F2:G5 B8:D11 F8:G11 B14:D17 F14:G17 B20:D23 F20:G23 B26:D29 F26:G29 B32:D35 F32:G35 B38:D41 F38:G41 B44:D47 F44:G47 B50:D53 F50:G53 B56:D59 F56:G59 B62:D65" name="Group Stage Results"/>
   </protectedRanges>
+  <mergeCells count="2">
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="N2:Y13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6628,18 +6988,18 @@
   <sheetData>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -6652,18 +7012,18 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -6676,18 +7036,18 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="W10" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="W11" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
@@ -6697,134 +7057,136 @@
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
       <c r="J13" s="59"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="61"/>
+      <c r="K13" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="L13" s="75"/>
+      <c r="M13" s="76"/>
+      <c r="N13" s="60"/>
       <c r="U13" s="1"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" s="61"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="62"/>
+      <c r="W14" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="J14" s="62"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64"/>
-      <c r="W14" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G15" s="49"/>
       <c r="H15" s="50"/>
       <c r="I15" s="15"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="64"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="62"/>
       <c r="P15" s="49"/>
       <c r="Q15" s="50"/>
       <c r="W15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="G16" s="51"/>
       <c r="H16" s="52"/>
       <c r="I16" s="15"/>
-      <c r="J16" s="67"/>
+      <c r="J16" s="65"/>
       <c r="K16" s="50"/>
-      <c r="L16" s="66"/>
+      <c r="L16" s="64"/>
       <c r="M16" s="49"/>
-      <c r="N16" s="68"/>
+      <c r="N16" s="66"/>
       <c r="P16" s="51"/>
       <c r="Q16" s="52"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="J17" s="69"/>
+      <c r="J17" s="67"/>
       <c r="K17" s="54"/>
-      <c r="L17" s="66" t="s">
-        <v>104</v>
+      <c r="L17" s="64" t="s">
+        <v>103</v>
       </c>
       <c r="M17" s="53"/>
-      <c r="N17" s="70"/>
+      <c r="N17" s="68"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G18" s="49"/>
       <c r="H18" s="50"/>
       <c r="I18" s="15"/>
-      <c r="J18" s="71"/>
+      <c r="J18" s="69"/>
       <c r="K18" s="52"/>
-      <c r="L18" s="66"/>
+      <c r="L18" s="64"/>
       <c r="M18" s="51"/>
-      <c r="N18" s="72"/>
+      <c r="N18" s="70"/>
       <c r="P18" s="49"/>
       <c r="Q18" s="50"/>
       <c r="W18" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G19" s="51"/>
       <c r="H19" s="52"/>
       <c r="I19" s="15"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="64"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="62"/>
       <c r="P19" s="51"/>
       <c r="Q19" s="52"/>
       <c r="W19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="76" t="s">
-        <v>180</v>
-      </c>
-      <c r="L20" s="77"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="64"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="L20" s="75"/>
+      <c r="M20" s="76"/>
+      <c r="N20" s="62"/>
       <c r="U20" s="1"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
-      <c r="J21" s="73"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="75"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="73"/>
       <c r="U21" s="1"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="W22" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="W23" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
@@ -6837,18 +7199,18 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W26" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="W27" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
@@ -6861,23 +7223,24 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="W30" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="W31" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="W31" s="1" t="s">
-        <v>120</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="K20:M21"/>
+    <mergeCell ref="K13:M14"/>
     <mergeCell ref="G15:H16"/>
     <mergeCell ref="G18:H19"/>
     <mergeCell ref="P15:Q16"/>
@@ -6903,24 +7266,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C1" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="55" t="s">
         <v>123</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C2" s="21" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w40/" &amp; LOWER(B2)&amp; ".png")</f>
@@ -6932,10 +7295,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="18" t="e" vm="2">
         <f t="shared" ref="C3:C49" si="0">_xlfn.IMAGE("https://flagcdn.com/w40/" &amp; LOWER(B3)&amp; ".png")</f>
@@ -6947,10 +7310,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" s="18" t="e" vm="3">
         <f t="shared" si="0"/>
@@ -6962,10 +7325,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="18" t="e" vm="4">
         <f t="shared" si="0"/>
@@ -6977,10 +7340,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>129</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>130</v>
       </c>
       <c r="C6" s="18" t="e" vm="5">
         <f t="shared" si="0"/>
@@ -6992,10 +7355,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="18" t="e" vm="6">
         <f t="shared" si="0"/>
@@ -7007,10 +7370,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="18" t="e" vm="7">
         <f t="shared" si="0"/>
@@ -7022,10 +7385,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C9" s="18" t="e" vm="8">
         <f t="shared" si="0"/>
@@ -7037,10 +7400,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="18" t="e" vm="9">
         <f t="shared" si="0"/>
@@ -7052,10 +7415,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="18" t="e" vm="10">
         <f t="shared" si="0"/>
@@ -7067,10 +7430,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="18" t="e" vm="11">
         <f t="shared" si="0"/>
@@ -7082,10 +7445,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13" s="18" t="e" vm="12">
         <f t="shared" si="0"/>
@@ -7097,10 +7460,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14" s="18" t="e" vm="13">
         <f t="shared" si="0"/>
@@ -7112,10 +7475,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="18" t="e" vm="14">
         <f t="shared" si="0"/>
@@ -7127,10 +7490,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="18" t="e" vm="15">
         <f t="shared" si="0"/>
@@ -7142,10 +7505,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="18" t="e" vm="16">
         <f t="shared" si="0"/>
@@ -7157,10 +7520,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="18" t="e" vm="17">
         <f t="shared" si="0"/>
@@ -7172,10 +7535,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="18" t="e" vm="18">
         <f t="shared" si="0"/>
@@ -7187,10 +7550,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="18" t="e" vm="19">
         <f t="shared" si="0"/>
@@ -7202,10 +7565,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="18" t="e" vm="20">
         <f t="shared" si="0"/>
@@ -7217,10 +7580,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="18" t="e" vm="21">
         <f t="shared" si="0"/>
@@ -7232,10 +7595,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="18" t="e" vm="22">
         <f t="shared" si="0"/>
@@ -7247,10 +7610,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C24" s="18" t="e" vm="23">
         <f t="shared" si="0"/>
@@ -7262,10 +7625,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="18" t="e" vm="24">
         <f t="shared" si="0"/>
@@ -7277,10 +7640,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C26" s="18" t="e" vm="25">
         <f t="shared" si="0"/>
@@ -7292,10 +7655,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C27" s="18" t="e" vm="26">
         <f t="shared" si="0"/>
@@ -7307,10 +7670,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="18" t="e" vm="27">
         <f t="shared" si="0"/>
@@ -7322,10 +7685,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C29" s="18" t="e" vm="28">
         <f t="shared" si="0"/>
@@ -7337,10 +7700,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>154</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>155</v>
       </c>
       <c r="C30" s="18" t="e" vm="29">
         <f t="shared" si="0"/>
@@ -7352,10 +7715,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C31" s="18" t="e" vm="30">
         <f t="shared" si="0"/>
@@ -7367,10 +7730,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C32" s="18" t="e" vm="31">
         <f t="shared" si="0"/>
@@ -7382,10 +7745,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C33" s="18" t="e" vm="32">
         <f t="shared" si="0"/>
@@ -7397,10 +7760,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C34" s="18" t="e" vm="33">
         <f t="shared" si="0"/>
@@ -7412,10 +7775,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="18" t="s">
         <v>160</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>161</v>
       </c>
       <c r="C35" s="18" t="e" vm="34">
         <f t="shared" si="0"/>
@@ -7427,10 +7790,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C36" s="18" t="e" vm="35">
         <f t="shared" si="0"/>
@@ -7442,10 +7805,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C37" s="18" t="e" vm="36">
         <f t="shared" si="0"/>
@@ -7457,10 +7820,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C38" s="18" t="e" vm="37">
         <f t="shared" si="0"/>
@@ -7472,10 +7835,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C39" s="18" t="e" vm="38">
         <f t="shared" si="0"/>
@@ -7487,10 +7850,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" s="18" t="s">
         <v>166</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>167</v>
       </c>
       <c r="C40" s="18" t="e" vm="39">
         <f t="shared" si="0"/>
@@ -7502,10 +7865,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C41" s="18" t="e" vm="40">
         <f t="shared" si="0"/>
@@ -7517,10 +7880,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" s="18" t="e" vm="41">
         <f t="shared" si="0"/>
@@ -7532,10 +7895,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="18" t="e" vm="42">
         <f t="shared" si="0"/>
@@ -7547,10 +7910,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C44" s="18" t="e" vm="43">
         <f t="shared" si="0"/>
@@ -7562,10 +7925,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C45" s="18" t="e" vm="44">
         <f t="shared" si="0"/>
@@ -7577,10 +7940,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C46" s="18" t="e" vm="45">
         <f t="shared" si="0"/>
@@ -7592,10 +7955,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C47" s="18" t="e" vm="46">
         <f t="shared" si="0"/>
@@ -7607,10 +7970,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" s="18" t="e" vm="47">
         <f t="shared" si="0"/>
@@ -7622,10 +7985,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C49" s="18" t="e" vm="48">
         <f t="shared" si="0"/>
@@ -7652,13 +8015,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" t="s">
         <v>177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>178</v>
-      </c>
-      <c r="C1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">

--- a/World Cup 2026 SweepStake Template.xlsx
+++ b/World Cup 2026 SweepStake Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvfile01\Users\bobby.blaney\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8298577-4561-4939-AADD-8947DCDE8CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8A3108-29CE-478D-A7D5-F89CFA052BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -551,7 +551,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="183">
   <si>
     <t>Sweepstake 1</t>
   </si>
@@ -1227,6 +1227,108 @@
 Goal difference will need to be manually added, and can be found in the live group tables.
 Biggest defeat is to record each teams biggest loss, to identify the bogey prize winner for this category.
 Winners for each group, Runner up and 3rd place will all auto populate to help you fill in the Knockouts table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Once you have identified all participats and drawn/allocated teams, fill in the sweepstake tables on the left with all drawn names and teams.
+Fill in the correct </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Entry Fee</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sweepstakes Active </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">fields… This will calculate prize values for you above.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">N.b </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">If you juts want a basic, 1 draw for all 48 teams; only populate Sweepstake 1 and Team 1 columns and ensure you change </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sweepstakes Active</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
     </r>
   </si>
 </sst>
@@ -1988,7 +2090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2147,6 +2249,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4799,7 +4904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18FCF8B-6979-46D2-A22D-0412E8EA3650}">
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -5362,7 +5467,7 @@
       <c r="W24" s="42"/>
       <c r="X24" s="43"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5383,13 +5488,128 @@
       <c r="I26" s="13"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
+      <c r="M26" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="45"/>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="X26" s="46"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M27" s="79" t="s">
+        <v>182</v>
+      </c>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="39"/>
+      <c r="V27" s="39"/>
+      <c r="W27" s="39"/>
+      <c r="X27" s="40"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M28" s="38"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="39"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="40"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M29" s="38"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="40"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M30" s="38"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="39"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="39"/>
+      <c r="V30" s="39"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="40"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M31" s="38"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="40"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M32" s="38"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="39"/>
+      <c r="S32" s="39"/>
+      <c r="T32" s="39"/>
+      <c r="U32" s="39"/>
+      <c r="V32" s="39"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="40"/>
+    </row>
+    <row r="33" spans="13:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="41"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="42"/>
+      <c r="V33" s="42"/>
+      <c r="W33" s="42"/>
+      <c r="X33" s="43"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A3:K51 P1 R1" name="Range1"/>
   </protectedRanges>
-  <mergeCells count="9">
+  <mergeCells count="11">
+    <mergeCell ref="M26:X26"/>
+    <mergeCell ref="M27:X33"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="M1:N1"/>
@@ -5446,20 +5666,20 @@
       <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="80" t="s">
+      <c r="N1" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="83"/>
     </row>
     <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -5481,20 +5701,20 @@
         <f t="array" ref="J2">INDEX(A2:A5,MATCH(LARGE(B2:B5+C2:C5+D2:D5,1),B2:B5+C2:C5+D2:D5,0))</f>
         <v>Mexico</v>
       </c>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="84" t="s">
         <v>181</v>
       </c>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="84"/>
-      <c r="S2" s="84"/>
-      <c r="T2" s="84"/>
-      <c r="U2" s="84"/>
-      <c r="V2" s="84"/>
-      <c r="W2" s="84"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="85"/>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="86"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -5516,18 +5736,18 @@
         <f t="array" ref="J3">INDEX(A2:A5,MATCH(LARGE(B2:B5+C2:C5+D2:D5,2),B2:B5+C2:C5+D2:D5,0))</f>
         <v>Mexico</v>
       </c>
-      <c r="N3" s="86"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="88"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -5553,18 +5773,18 @@
         <f>LARGE(E2:E5,3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="86"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79"/>
-      <c r="V4" s="79"/>
-      <c r="W4" s="79"/>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="87"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="88"/>
     </row>
     <row r="5" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -5579,18 +5799,18 @@
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="79"/>
-      <c r="U5" s="79"/>
-      <c r="V5" s="79"/>
-      <c r="W5" s="79"/>
-      <c r="X5" s="79"/>
-      <c r="Y5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
+      <c r="V5" s="80"/>
+      <c r="W5" s="80"/>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="88"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
@@ -5600,18 +5820,18 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
-      <c r="V6" s="79"/>
-      <c r="W6" s="79"/>
-      <c r="X6" s="79"/>
-      <c r="Y6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
+      <c r="V6" s="80"/>
+      <c r="W6" s="80"/>
+      <c r="X6" s="80"/>
+      <c r="Y6" s="88"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -5638,18 +5858,18 @@
       <c r="I7" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="86"/>
-      <c r="O7" s="79"/>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="79"/>
-      <c r="R7" s="79"/>
-      <c r="S7" s="79"/>
-      <c r="T7" s="79"/>
-      <c r="U7" s="79"/>
-      <c r="V7" s="79"/>
-      <c r="W7" s="79"/>
-      <c r="X7" s="79"/>
-      <c r="Y7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80"/>
+      <c r="T7" s="80"/>
+      <c r="U7" s="80"/>
+      <c r="V7" s="80"/>
+      <c r="W7" s="80"/>
+      <c r="X7" s="80"/>
+      <c r="Y7" s="88"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -5671,18 +5891,18 @@
         <f t="array" ref="J8">INDEX(A8:A11,MATCH(LARGE(B8:B11+C8:C11+D8:D11,1),B8:B11+C8:C11+D8:D11,0))</f>
         <v>Canada</v>
       </c>
-      <c r="N8" s="86"/>
-      <c r="O8" s="79"/>
-      <c r="P8" s="79"/>
-      <c r="Q8" s="79"/>
-      <c r="R8" s="79"/>
-      <c r="S8" s="79"/>
-      <c r="T8" s="79"/>
-      <c r="U8" s="79"/>
-      <c r="V8" s="79"/>
-      <c r="W8" s="79"/>
-      <c r="X8" s="79"/>
-      <c r="Y8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="80"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="80"/>
+      <c r="X8" s="80"/>
+      <c r="Y8" s="88"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -5704,18 +5924,18 @@
         <f t="array" ref="J9">INDEX(A8:A11,MATCH(LARGE(B8:B11+C8:C11+D8:D11,2),B8:B11+C8:C11+D8:D11,0))</f>
         <v>Canada</v>
       </c>
-      <c r="N9" s="86"/>
-      <c r="O9" s="79"/>
-      <c r="P9" s="79"/>
-      <c r="Q9" s="79"/>
-      <c r="R9" s="79"/>
-      <c r="S9" s="79"/>
-      <c r="T9" s="79"/>
-      <c r="U9" s="79"/>
-      <c r="V9" s="79"/>
-      <c r="W9" s="79"/>
-      <c r="X9" s="79"/>
-      <c r="Y9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="80"/>
+      <c r="X9" s="80"/>
+      <c r="Y9" s="88"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -5741,18 +5961,18 @@
         <f>LARGE(E8:E11,3)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="86"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="79"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="79"/>
-      <c r="U10" s="79"/>
-      <c r="V10" s="79"/>
-      <c r="W10" s="79"/>
-      <c r="X10" s="79"/>
-      <c r="Y10" s="87"/>
+      <c r="N10" s="87"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+      <c r="R10" s="80"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="80"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="88"/>
     </row>
     <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -5767,18 +5987,18 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7"/>
-      <c r="N11" s="86"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="79"/>
-      <c r="S11" s="79"/>
-      <c r="T11" s="79"/>
-      <c r="U11" s="79"/>
-      <c r="V11" s="79"/>
-      <c r="W11" s="79"/>
-      <c r="X11" s="79"/>
-      <c r="Y11" s="87"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="88"/>
     </row>
     <row r="12" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
@@ -5788,18 +6008,18 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="79"/>
-      <c r="U12" s="79"/>
-      <c r="V12" s="79"/>
-      <c r="W12" s="79"/>
-      <c r="X12" s="79"/>
-      <c r="Y12" s="87"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="80"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="80"/>
+      <c r="X12" s="80"/>
+      <c r="Y12" s="88"/>
     </row>
     <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -5826,18 +6046,18 @@
       <c r="I13" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="88"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="89"/>
-      <c r="T13" s="89"/>
-      <c r="U13" s="89"/>
-      <c r="V13" s="89"/>
-      <c r="W13" s="89"/>
-      <c r="X13" s="89"/>
-      <c r="Y13" s="90"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="90"/>
+      <c r="W13" s="90"/>
+      <c r="X13" s="90"/>
+      <c r="Y13" s="91"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
